--- a/Programowanie równoległe/lab_13/ryzen 5 7600X.xlsx
+++ b/Programowanie równoległe/lab_13/ryzen 5 7600X.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\Programowanie równoległe\lab_13\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED1FB708-C767-400A-92B8-D1178AFCA537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944D029C-167B-4FD8-8335-ABBD7E734C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{83BCF7F2-8C3D-422A-8B56-2EA3527EE29E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{83BCF7F2-8C3D-422A-8B56-2EA3527EE29E}"/>
   </bookViews>
   <sheets>
     <sheet name="calka" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="169" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000000000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -219,14 +219,14 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1213,7 +1213,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL"/>
-                  <a:t>Czas</a:t>
+                  <a:t>Czas[s]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2887,7 +2887,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="pl-PL"/>
-                  <a:t>Czas</a:t>
+                  <a:t>Czas[s]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -7173,10 +7173,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -7495,215 +7491,215 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35C23A2F-987C-40ED-B07B-25866A6997F2}">
   <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="8.5546875" customWidth="1"/>
+    <col min="17" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2">
         <v>4</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2">
         <v>6</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2">
         <v>8</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2">
         <v>12</v>
       </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>7.6688999999999993E-2</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>7.7784000000000006E-2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>7.6582999999999998E-2</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>3.8438E-2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>3.8137999999999998E-2</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>3.814E-2</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>1.9349000000000002E-2</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>1.9630000000000002E-2</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>2.0121E-2</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>2.7331999999999999E-2</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>2.7754999999999998E-2</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>2.1073999999999999E-2</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <v>2.1037E-2</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <v>2.1576999999999999E-2</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>2.1603000000000001E-2</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>1.7139999999999999E-2</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>1.6795000000000001E-2</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>1.7191999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>0.25000000000001199</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
         <v>0.24999999999998901</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
         <v>0.24999999999999101</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3">
         <v>0.24999999999998601</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4">
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <v>0.25000000000000899</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4">
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3">
         <v>0.25000000000001199</v>
       </c>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <f>AVERAGE(B3:D3)</f>
         <v>7.7018666666666666E-2</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="3">
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="4">
         <f t="shared" ref="E5" si="0">AVERAGE(E3:G3)</f>
         <v>3.8238666666666671E-2</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="3">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="4">
         <f t="shared" ref="H5" si="1">AVERAGE(H3:J3)</f>
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="3">
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="4">
         <f t="shared" ref="K5" si="2">AVERAGE(K3:M3)</f>
         <v>2.5386999999999996E-2</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4">
         <f>AVERAGE(N3:P3)</f>
         <v>2.1405666666666667E-2</v>
       </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3">
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4">
         <f t="shared" ref="Q5" si="3">AVERAGE(Q3:S3)</f>
         <v>1.7042333333333333E-2</v>
       </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -7723,11 +7719,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <f>B5</f>
         <v>7.7018666666666666E-2</v>
       </c>
@@ -7747,11 +7743,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <f>E5</f>
         <v>3.8238666666666671E-2</v>
       </c>
@@ -7771,11 +7767,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>4</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <f>H5</f>
         <v>1.9699999999999999E-2</v>
       </c>
@@ -7795,11 +7791,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>6</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <f>K5</f>
         <v>2.5386999999999996E-2</v>
       </c>
@@ -7819,11 +7815,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>8</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <f>N5</f>
         <v>2.1405666666666667E-2</v>
       </c>
@@ -7843,11 +7839,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>12</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <f>Q5</f>
         <v>1.7042333333333333E-2</v>
       </c>
@@ -7869,13 +7865,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N5:P5"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
     <mergeCell ref="Q5:S5"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="B2:D2"/>
@@ -7888,6 +7877,13 @@
     <mergeCell ref="H4:J4"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7898,179 +7894,179 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1AA98E5-0E45-4F7E-8797-96C5F81B9857}">
   <dimension ref="A1:S14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="17" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
         <v>2</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2">
         <v>4</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2">
         <v>6</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2">
         <v>8</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1">
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2">
         <v>12</v>
       </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>6.5575999999999995E-2</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>6.4551999999999998E-2</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>6.4332E-2</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>3.2111000000000001E-2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>3.1338999999999999E-2</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="1">
         <v>3.2001000000000002E-2</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="1">
         <v>1.6802000000000001E-2</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="1">
         <v>1.636E-2</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>1.6879000000000002E-2</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="1">
         <v>1.5681E-2</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="1">
         <v>1.5868E-2</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="1">
         <v>1.5803999999999999E-2</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="1">
         <v>1.4569E-2</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
         <v>1.5429999999999999E-2</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="1">
         <v>1.5219E-2</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="1">
         <v>1.6337999999999998E-2</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="1">
         <v>1.5606E-2</v>
       </c>
-      <c r="S3" s="2">
+      <c r="S3" s="1">
         <v>1.5831999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <f>AVERAGE(B3:D3)</f>
         <v>6.4820000000000003E-2</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="3">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="4">
         <f>AVERAGE(E3:G3)</f>
         <v>3.1817000000000005E-2</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="3">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="4">
         <f>AVERAGE(H3:J3)</f>
         <v>1.6680333333333335E-2</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="3">
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="4">
         <f>AVERAGE(K3:M3)</f>
         <v>1.5784333333333334E-2</v>
       </c>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4">
         <f>AVERAGE(N3:P3)</f>
         <v>1.5072666666666665E-2</v>
       </c>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3">
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4">
         <f>AVERAGE(Q3:S3)</f>
         <v>1.5925333333333333E-2</v>
       </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -8090,11 +8086,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <f>B4</f>
         <v>6.4820000000000003E-2</v>
       </c>
@@ -8114,11 +8110,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <f>E4</f>
         <v>3.1817000000000005E-2</v>
       </c>
@@ -8138,11 +8134,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <f>H4</f>
         <v>1.6680333333333335E-2</v>
       </c>
@@ -8162,11 +8158,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>6</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <f>K4</f>
         <v>1.5784333333333334E-2</v>
       </c>
@@ -8186,11 +8182,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>8</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <f>N4</f>
         <v>1.5072666666666665E-2</v>
       </c>
@@ -8210,11 +8206,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <f>Q4</f>
         <v>1.5925333333333333E-2</v>
       </c>
@@ -8236,11 +8232,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="N4:P4"/>
     <mergeCell ref="Q4:S4"/>
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="B2:D2"/>
@@ -8249,6 +8240,11 @@
     <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="N4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
